--- a/output/full_scan/batch_seq8_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-12.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,12 +60,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -428,23 +436,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -527,107 +535,6785 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
+        <v>6944</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>兆聯實業</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1425.53336072647</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>991</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>61.7665887908777</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>12.6995573453634</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>2.553336072646994</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>2.651812390923861</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>7721</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>微程式</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1214.226653285008</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>56.70592826451681</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>15.23575623908191</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1.922665328500788</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.2217790900144564</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>8048</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>德勝</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1180.478665407518</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>58.77744668395371</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>17.78142640733082</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>2.547866540751828</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.210316132612204</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>8021</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>尖點</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>906.8892634762065</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>522</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>59.58603378799089</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>18.50836348934918</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>3.188926347620648</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>8.406846399275384</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>8044</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>網家</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>888.6075642862021</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>57.51617837700001</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>32.07191072006574</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.3607564286202127</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>-0.1028898755236766</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>8042</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>金山電</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>884.3689078601427</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>70.25197987194618</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>38.999878711784</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.9368907860142666</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>-1.392181246768498</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6922</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>宸曜</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>861.7266758882209</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>50.85078296589673</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>27.3696327448796</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.6726675888220953</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-1.411060548783434</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7769</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>837.9939362569963</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7210</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>55.01613477686069</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>30.49850412982849</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.7993936256996366</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>-160.6275350480506</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>7788</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>松川精密</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>834.8567609946067</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>72.94173774481709</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>39.87863451824048</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1.485676099460668</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>7.130749145370062</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>8016</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>832.7061440433425</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>54.61477490476519</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>51.57121664155368</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.770614404334254</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-4.304178393060349</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>6949</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沛爾生醫-創</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>828.3294387018015</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>56.68930185846356</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>20.31799957448061</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.8329438701801496</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>8.221633328659241</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>6901</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>鑽石投資</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>824.3488348188021</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>69.06785459057467</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>29.93075363685241</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.9348834818802024</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0.3520695599072441</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>8043</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>蜜望實</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>821.1602427676717</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>70.21820882110732</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>42.86575644197554</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.116024276767161</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>3.824141630143771</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>8028</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>昇陽半導體</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>819.6830379623452</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>56.3559937500084</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>45.02740309674527</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.4683037962345187</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>-5.337304864523681</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>6870</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>騰雲</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>810.6548469465419</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>65.38422920739143</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>34.87028377448986</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.5654846946541823</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>2.075766362309711</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>7722</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LINEPAY</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>800.6546263863687</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>61.55334469752472</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>37.27326639858043</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>3.065462638636868</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>10.7702467025557</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>6957</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>裕慶-KY</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>785.4908797840318</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>68.25456176667758</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>30.70548225237109</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.5490879784031752</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1.425570971862109</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>6907</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>雅特力-KY</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>781.8627969691015</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>55.04847974557215</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>29.74443408614899</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.6862796969101508</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.6942950527814089</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>6996</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>力領科技</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>780.1621672707291</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>56.17616191515894</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>30.59568105525484</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.516216727072912</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.2549277233091684</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>8039</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>台虹</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>756.177136890076</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>54.99184160427471</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>26.4639942420312</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1.117713689007603</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>-1.487896207936378</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>6899</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>創為精密</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>731.6422747673743</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>52.44072641438644</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>25.3460217506559</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.1642274767374211</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>-0.5709587845424289</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>7749</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>意騰-KY</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>724.7298403504723</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>54.13543700364139</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>25.56391217794169</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.4729840350472238</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>-1.267404474986231</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>7827</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>漢康-KY創</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>709.1928891006829</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>61.32311511764907</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>21.73455210917072</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.4192889100682876</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1.020375528874119</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>7750</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>新代</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>702.9739982648821</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>47.37767386624609</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>25.0575184367815</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.7973998264882118</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>-43.3730656432022</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>7780</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>大研生醫*</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>678.9318828820424</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>54.89286899032182</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>20.90192406219033</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1.393188288204242</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0.2210038415836543</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
         <v>7610</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>聯友金屬-創</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>677.959716532622</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E27" s="2" t="n">
         <v>1590</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
         <v>62.70709408550278</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>61.95889148382133</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>0.7959716532622049</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N2" s="2" t="n">
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" s="2" t="n">
         <v>-15.26912122409442</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>7744</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>崴寶</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>674.7166193656333</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>49.02881556596995</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>16.11260058454811</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.9716619365633276</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.0615858643475046</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>8032</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>光菱</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>668.7897601473858</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>51.81798038516452</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>28.31128155224281</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.3789760147385796</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>-0.4310528142663705</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>6965</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>中傑-KY</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>624.1480164590173</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>55.90829287628868</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>22.23150851948611</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.4148016459017333</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.6147632119361368</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>6903</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>巨漢</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>620.0096295811835</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>51.46778531473922</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>19.25610989948265</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1.000962958118349</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>-3.333084676460954</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>7712</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>博盛半導體</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>608.8848916425136</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>46.32296692967262</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>21.89785232661185</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.3884891642513539</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>-4.190795343884508</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>6906</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>現觀科</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>593.4979362660481</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>53.88408330804492</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>35.73523631094107</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.3497936266048155</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>-1.764057556695946</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>6931</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>青松健康</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>574.979553425174</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>43.12537913867094</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>32.45543512289591</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.4979553425174027</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.4055706108728902</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>6894</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>衛司特</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>559.0227951595966</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>45.84065622649885</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>26.7332505885146</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.4022795159596701</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-5.451107162819186</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>7711</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>永擎</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>538.7844657009132</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>44.40496188049803</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>18.20946658960669</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.3784465700913173</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>-6.132480457292956</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>6924</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>榮惠-KY創</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>530.2458997357785</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>37.5020583846748</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>44.75934923755536</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1.024589973577847</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>-9.151246349591011</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>6916</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>華凌</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>525.134912428405</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>54.54728839313233</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>27.22050420477196</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1.013491242840488</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.1774846538979639</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>6861</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>睿生光電</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>519.0616642657129</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>38.86742570119624</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>35.2995805041555</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.406166426571294</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>-18.77933386405595</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
         <v>6890</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>來億-KY</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="C40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="n">
         <v>511.6384873419656</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E40" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
         <v>71.01426355117248</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>42.00841338763109</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J40" s="2" t="n">
         <v>0.1638487341965594</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N3" s="2" t="n">
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" s="2" t="n">
         <v>8.991888238979282</v>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>8040</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>九暘</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>509.3482516064997</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>49.34245541329533</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>38.42220158885928</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.4348251606499724</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-3.215677468792008</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>6902</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>GOGOLOOK</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>508.1768598879146</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>52.84439776212625</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>40.28634227269063</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.3176859887914597</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-2.122835049996312</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>7765</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>中華資安</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>505.374719368347</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>48.57086337061394</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>33.21389484921666</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.5374719368346998</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-1.857165094156166</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>6859</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>伯特光</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>500.0407619110457</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>51.05087233540092</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>24.23630293481606</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1.004076191104569</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-0.3481416810093281</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>6918</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>愛派司</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>483.8825951386297</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>46.84626594154159</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>9.070415866578839</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.3882595138629715</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>-0.011514727523934</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>7768</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>頌勝科技</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>478.1438681253589</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>45.10980818715755</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>16.49432684445235</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.3143868125358912</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>-1.269825580910085</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>6855</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>數泓科</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>466.7764856740154</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>56.68658556669776</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15.30592346154639</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.1776485674015408</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0.286275210752807</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>6958</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>日盛台駿</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>464.1104318422929</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>47.72993703673042</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>20.77106986409033</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.411043184229294</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0.0564613944359488</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>7732</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>金興精密</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>462.7841000048722</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>53.73707106607963</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>13.41529191144591</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.2784100004872175</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-0.0005430706224374</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>6937</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>天虹</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>461.2319415376433</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>276.5</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>42.8519127728765</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15.63849968715516</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.6231941537643236</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>-4.039124766122492</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>460.607962367113</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>49.70843798488475</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>21.13005376284863</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.0607962367113</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-0.1465798453579647</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>7747</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>昕奇雲端</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>458.170237649343</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>51.37628265179114</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>9.230295611189378</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>2.317023764934301</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0.7374812384260343</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>7795</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>長廣</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>452.2087316229014</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>47.97187933462748</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15.484877462497</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.7208731622901393</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>-3.885561456561167</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>6925</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>意藍</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>451.9137579874425</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>46.80668540012381</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>27.24046596843369</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.6913757987442459</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.5238784722489074</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>7738</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>東聯互動</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>441.8543828323637</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>48.68952557441283</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>20.55413394846869</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.6854382832363759</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0.5652667828907383</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>6909</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>創控</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>440.9394429651246</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>33.5610800431983</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>20.97308408535397</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.593944296512459</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>-0.833355335643323</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>7734</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>印能科技</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>431.74698875803</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>37.78211081606065</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>25.56495685642648</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>2.174698875802998</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>-83.10892122765549</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>7704</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>明遠精密</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>429.3588243033201</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>48.28262045318248</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>14.81795505161054</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.4358824303320083</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>-0.449183760554575</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>7730</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>暉盛-創</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>428.8928546105946</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>42.37638104607336</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>20.71388053674854</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.3892854610594629</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-4.718263705964227</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>7786</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>東方風能</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>426.4687849208649</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>53.40936791324678</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>19.3810818987944</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.146878492086497</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1.663927406624419</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>7705</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>三商餐飲</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>425.0933807226314</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>47.69803809664406</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>20.41023967958111</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.5093380722631434</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0.127244794733756</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>8038</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>長園科</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>424.6135014493271</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>49.34457901831322</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>9.763920474886024</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.961350144932708</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0.0766462047627977</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>6913</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>鴻呈</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>417.5032792103642</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>41.37354641578403</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>20.15285200280358</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.2503279210364211</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-2.233376056149653</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>7805</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>威聯通</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>414.8806099717826</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>39.58503808614317</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>30.0359276128329</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.4880609971782658</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-12.03380295215134</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>6862</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>三集瑞-KY</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>411.6235748102233</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>50.39381357567824</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>23.46635952558299</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.6623574810223247</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>-0.983947996562935</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>7760</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>享溫馨</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>410.8743527461241</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>38.00031268280768</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>58.00267243258273</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.5874352746124096</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.1147035085436186</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>7556</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>意德士</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>410.0538808323726</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>50.09172604156009</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>17.80609732360519</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.5053880832372599</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-2.092027328525888</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>7792</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>安葆</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>408.8964399919968</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>37.07209713454611</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>23.24507526220753</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.3896439991996754</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-0.4604206677264812</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>7822</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>倍利科</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>407.273590943246</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>40.32434245732718</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>15.29467297457212</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.7273590943245991</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-1.471145654592391</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>6887</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>寶綠特-KY</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>401.7447700277428</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>49.81440382669898</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>8.041034342324371</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.1744770027742807</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0.4298381996656945</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>8047</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>星雲</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>395.4861264174447</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>53.79683764007137</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>8.724222300257962</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.5486126417444738</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>1.109473453085746</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>6914</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>阜爾運通</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>395.017636215438</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>48.62736634903472</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>15.69688334800572</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.5017636215437998</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0.2564899145381347</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>7703</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>銳澤</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>391.9548127125473</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>48.34189137153759</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>16.25965699660846</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.6954812712547341</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.9591103584465568</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>7631</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>聚賢研發-創</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>391.5984320976953</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>51.52776260167308</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>11.36712557381713</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1.159843209769534</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>1.692053124409412</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>6865</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>偉康科技</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>390.0213647967835</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>48.40992118191884</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>29.64609098156348</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>2.502136479678348</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.1158300015841296</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>6962</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>奕力-KY</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>384.7736620038214</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>47.25201804911922</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>14.13074368714482</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.477366200382143</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>-0.4283411339741368</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>7714</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>創泓科技</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>378.4421180333328</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>50.51844173301552</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>25.46467647229126</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.3442118033332742</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0.8309296535801629</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>7717</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>萊德光電-KY</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>376.2024803949569</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>42.4977868842211</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>14.46636211378523</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1.120248039495693</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-2.579669424909881</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>8033</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>雷虎</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>375.2081370738664</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>41.80367068976801</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>7.950165023926123</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.5208137073866317</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.6051505216775852</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>7799</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>禾榮科</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>375.0361875039968</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>50.28857848156903</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>26.51819851052429</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.503618750399683</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>3.283903418336756</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>7803</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>雲象科技-創</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>373.9298991590181</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>37.26291934233446</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>23.00406673708863</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.3929899159018113</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.198012066470971</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>7821</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>神數</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>367.2943262090122</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>43.59106620764173</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>21.10376004189162</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.7294326209012251</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.3846562261460666</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6936</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>永鴻生技</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>361.7393621975403</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>48.4483783289348</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>12.76939815275165</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.6739362197540264</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.0400490343138349</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>8034</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>榮群</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>351.5143286817366</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>41.90625936726997</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>16.72692438226106</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.6514328681736635</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.1078838719709018</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>7772</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>耀穎</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>339.1706380326398</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>42.16685151138954</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>11.78146341796022</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.4170638032639765</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-1.308344292912517</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>7751</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>竑騰</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>338.6711792868691</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>1375</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>37.69219704704503</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>19.50764444817833</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.8671179286869081</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-28.62189056360634</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>7728</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>光焱科技</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>327.6069599898044</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>714</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46.33940275328286</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>9.956476197835496</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.7606959989804409</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-2.913845945088823</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6953</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>家碩</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>327.0631187693833</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>44.48887598013136</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>19.04397864675919</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.206311876938332</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-2.898196210491274</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6923</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>中台</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>323.2532667975285</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>46.29672602559531</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>14.35623404935014</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.3253266797528472</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.1863080335182548</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>8046</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>317.5129034584801</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>46.80936630029059</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>18.62381595890087</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.751290345848006</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-11.71770609495905</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>7820</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>立盈</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>314.5773508988849</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>31.65601185854095</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>31.76411237648887</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.457735089888491</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.4435990523077961</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6967</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>汎瑋材料</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>308.3534709316485</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>45.66695313914724</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>9.881505434081944</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.3353470931648459</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.1077500860445618</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6921</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>嘉雨思-創</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>302.9052371244609</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>33.13873914380856</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>26.41252388308151</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.2905237124460855</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.406974632874499</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6951</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>青新-創</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>302.7028355489105</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>42.97282710947994</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>27.16735256673607</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.270283554891049</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.239468880788861</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6895</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>宏碩系統</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>297.2344617025655</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>53.87958355829369</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>20.5267251434022</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.7234461702565477</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>2.562437988025197</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>8011</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>台通</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>292.4896339936021</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>46.54577140594733</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>17.73314921494443</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.7489633993602111</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0.0288064316413266</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>7715</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>裕山</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>288.3153185326018</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>45.5009332788948</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>19.91363470182283</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.8315318532601812</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-0.018891610907073</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6908</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>宏碁遊戲-創</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>286.7984673116414</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>45.6661667209078</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>10.4603675476441</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.179846731164143</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.139011931702798</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6910</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>德鴻</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>283.5581809235436</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>49.1710938853001</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>14.53296382975697</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.85581809235436</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0.1131193024128545</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6955</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>邦睿生技-創</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>282.7653248670057</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>48.77146016105467</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>4.492558714127553</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.276532486700575</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.307605206945974</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6969</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>成信實業*-創</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>279.3670095020103</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>35.46612563266359</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>20.08998545207042</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.436700950201033</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.0660131096753126</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>富威電力</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>278.2510552535676</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>39.66544652983568</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>19.80409246576268</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.3251055253567615</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.1064274542838479</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6928</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>攸泰科技</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>276.9360166041646</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>38.54338705197733</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>17.1436539820518</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1.193601660416461</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.3815878447217742</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6997</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>博弘</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>275.1083895767219</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>23.56607869734</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>10.00832331105472</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.0108389576721941</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-4.626590109559539</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6877</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>鏵友益</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>271.4519277305434</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>31.28561271739036</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>20.04772858557391</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.6451927730543433</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-3.918849658919301</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6869</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>雲豹能源</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>268.4091661545837</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>41.38465324333775</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>17.18797027600868</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.3409166154583636</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-0.397836866181024</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>7740</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>熙特爾-創</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>265.9812199064206</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>46.07252934292077</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>10.85093873980253</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.5981219906420656</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.4655855303181588</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>AMAX-KY</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>253.5939496879953</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>41.37124826168041</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>17.77665243796438</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.3593949687995363</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-2.862006376828164</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6983</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>華洋精機</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>252.6978349341288</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>41.63151159327897</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>15.20889645549262</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.2697834934128824</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-1.805993898026742</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>7736</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>虎山</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>251.1971617934597</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>45.1143331266731</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>17.27816225811488</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.6197161793459688</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.1878017551903019</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6952</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>大武山</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>250.874573763311</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>40.6400061083673</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>19.30299526253795</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.5874573763311055</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.0230810592231141</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6885</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>全福生技</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>235.5903401426825</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>48.33927249608464</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>25.87543082387615</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.5590340142682472</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.1003669416178525</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6919</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>康霈*</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>235.1801451838762</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>42.64855296146145</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>13.9113682949289</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.5180145183876189</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.66513179012395</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>7842</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>天能綠電</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>235.0935165001199</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>34.0798737855266</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>27.09624830373308</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.5093516500119918</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.9961073317394612</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6863</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>永道-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>220.9922587555751</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>36.53535254047353</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>22.32383673610962</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.5992258755575028</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-2.004592314751858</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>8024</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>佑華</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>220.9921159524559</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>36.05600372849255</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>21.42972106712035</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5992115952455895</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0312123861916893</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6854</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>錼創科技-KY創</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>217.4123513203062</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>38.98491030567855</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>16.18920745548389</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.2412351320306198</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-2.124185120948817</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>君曜</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>212.9513138616888</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>46.97519556469604</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>6.932141404006591</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.2951313861688784</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.0026243746765728</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>7823</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>奧義賽博-KY創</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>212.4900189214313</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30.46071759679407</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>28.75931933051219</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.2490018921431323</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-2.456260308453188</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>7547</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>碩網</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>211.0427982017339</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>39.62274497051918</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>16.06049168935067</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.1042798201733911</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-0.3508182307702272</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6988</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>威力暘-創</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>200.4349388725179</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>32.28686477652359</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>20.28791164901725</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.543493887251788</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.2486752345501293</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6873</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>泓德能源</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>197.0855902536261</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>38.26365167924639</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>14.36409232370733</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.7085590253626063</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.9748116265369432</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>8045</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>達運光電</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>194.7787737657613</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>38.7373486247747</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>16.81758374157859</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.4778773765761313</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.532345850375866</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>7810</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>捷創科技</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>191.5702573228506</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>39.36079513991619</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>17.21475390656485</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.1570257322850577</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-3.673835984908413</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>7818</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>溢泰實業</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>177.8430475957529</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>24.5724541805997</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>46.86033427917551</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.2843047595752863</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>1.010267503521792</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>7791</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>皇家可口</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>164.1979281730529</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>38.29058989844245</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>26.50907711376835</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.419792817305286</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.4493956517315807</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6934</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>心誠鎂</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>163.5077727198483</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>37.9928200388804</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>32.19453885093665</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.3507772719848309</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.004759199163713</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>邑錡</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>158.1626088611822</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>29.19377029722166</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>20.0112473305953</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>1.316260886118225</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.1837573841839619</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>6971</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>惠民實業</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>155.3972895793058</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>34.42747052926478</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>15.99543155756578</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.5397289579305811</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.0032770688003268</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq8_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-12.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O129"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1425.53336072647</v>
+        <v>1440.53336072647</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>991</v>
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.7665887908777</v>
+        <v>61.76658880480784</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.6995573453634</v>
+        <v>12.69955762495174</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.553336072646994</v>
@@ -578,7 +578,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.651812390923861</v>
+        <v>2.651812387871111</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1214.226653285008</v>
+        <v>1229.226653285008</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>81.8</v>
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>56.70592826451681</v>
+        <v>56.70592828959345</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>15.23575623908191</v>
+        <v>15.23575625189798</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>1.922665328500788</v>
@@ -631,7 +631,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.2217790900144564</v>
+        <v>0.2217790898045804</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -666,10 +666,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>58.77744668395371</v>
+        <v>58.77744673937482</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.78142640733082</v>
+        <v>17.78142676293457</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.547866540751828</v>
@@ -684,7 +684,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.210316132612204</v>
+        <v>0.2103161322306153</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>906.8892634762065</v>
+        <v>921.8892634762065</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>522</v>
@@ -719,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.58603378799089</v>
+        <v>59.58603378744183</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.50836348934918</v>
+        <v>18.50836365764029</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>3.188926347620648</v>
@@ -737,7 +737,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>8.406846399275384</v>
+        <v>8.406846399265845</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>888.6075642862021</v>
+        <v>903.607564286202</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>29.9</v>
@@ -772,10 +772,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.51617837700001</v>
+        <v>57.51617856716274</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32.07191072006574</v>
+        <v>32.07191091211855</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.3607564286202127</v>
@@ -790,7 +790,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1028898755236766</v>
+        <v>-0.1028898760483632</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.25197987194618</v>
+        <v>70.25197988192582</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38.999878711784</v>
+        <v>38.99987891774665</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.9368907860142666</v>
@@ -843,7 +843,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.392181246768498</v>
+        <v>-1.392181247083286</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>50.85078296589673</v>
+        <v>50.85078300207819</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.3696327448796</v>
+        <v>27.36963288463631</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.6726675888220953</v>
@@ -896,7 +896,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-1.411060548783434</v>
+        <v>-1.411060550595976</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7769</v>
+        <v>7788</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>837.9939362569963</v>
+        <v>849.8567609946067</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7210</v>
+        <v>266</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -931,49 +931,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.01613477686069</v>
+        <v>72.94173773927363</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.49850412982849</v>
+        <v>39.87863448326472</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7993936256996366</v>
+        <v>1.485676099460668</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-160.6275350480506</v>
+        <v>7.130749145751656</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7788</v>
+        <v>6949</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>834.8567609946067</v>
+        <v>843.3294387018015</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>266</v>
+        <v>717</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -984,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>72.94173774481709</v>
+        <v>56.68930186596068</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>39.87863451824048</v>
+        <v>20.31799970649944</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.485676099460668</v>
+        <v>0.8329438701801496</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>7.130749145370062</v>
+        <v>8.221633328086824</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8016</v>
+        <v>6901</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>832.7061440433425</v>
+        <v>839.3488348188021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>289.5</v>
+        <v>16.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1037,49 +1037,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>54.61477490476519</v>
+        <v>69.06785478253754</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>51.57121664155368</v>
+        <v>29.93075372204353</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.770614404334254</v>
+        <v>0.9348834818802024</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-4.304178393060349</v>
+        <v>0.3520695596592106</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6949</v>
+        <v>7769</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>828.3294387018015</v>
+        <v>837.9939362569963</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>717</v>
+        <v>7210</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1090,49 +1090,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.68930185846356</v>
+        <v>55.0161347842624</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.31799957448061</v>
+        <v>30.49850413361776</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8329438701801496</v>
+        <v>0.7993936256996366</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>8.221633328659241</v>
+        <v>-160.6275350516754</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6901</v>
+        <v>8043</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>824.3488348188021</v>
+        <v>836.1602427676717</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16.2</v>
+        <v>184.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1143,16 +1143,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.06785459057467</v>
+        <v>70.21820882981309</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.93075363685241</v>
+        <v>42.86575653182807</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9348834818802024</v>
+        <v>1.116024276767161</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1161,31 +1161,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3520695599072441</v>
+        <v>3.824141629914809</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8043</v>
+        <v>8016</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>821.1602427676717</v>
+        <v>832.7061440433425</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>184.5</v>
+        <v>289.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1196,49 +1196,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>70.21820882110732</v>
+        <v>54.61477494468568</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>42.86575644197554</v>
+        <v>51.57121667281787</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.116024276767161</v>
+        <v>0.770614404334254</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.824141630143771</v>
+        <v>-4.304178393918921</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8028</v>
+        <v>6870</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>819.6830379623452</v>
+        <v>825.6548469465419</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1249,49 +1249,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.3559937500084</v>
+        <v>65.38422923248599</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45.02740309674527</v>
+        <v>34.87028393001986</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4683037962345187</v>
+        <v>0.5654846946541823</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-5.337304864523681</v>
+        <v>2.075766360306389</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6870</v>
+        <v>8028</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>810.6548469465419</v>
+        <v>819.6830379623452</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1302,29 +1302,29 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>65.38422920739143</v>
+        <v>56.35599378701704</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.87028377448986</v>
+        <v>45.02740321307083</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5654846946541823</v>
+        <v>0.4683037962345187</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.075766362309711</v>
+        <v>-5.337304865286853</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>800.6546263863687</v>
+        <v>815.6546263863687</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>333.5</v>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.55334469752472</v>
+        <v>61.55334480520369</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>37.27326639858043</v>
+        <v>37.27326640736923</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>3.065462638636868</v>
@@ -1373,7 +1373,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>10.7702467025557</v>
+        <v>10.77024669740425</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>785.4908797840318</v>
+        <v>800.4908797840318</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>189.5</v>
@@ -1408,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.25456176667758</v>
+        <v>68.25456174431091</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.70548225237109</v>
+        <v>30.70548229361362</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.5490879784031752</v>
@@ -1426,7 +1426,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.425570971862109</v>
+        <v>1.425570971575902</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6907</v>
+        <v>6996</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>781.8627969691015</v>
+        <v>795.1621672707291</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>141</v>
+        <v>197.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1461,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.04847974557215</v>
+        <v>56.17616201422074</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>29.74443408614899</v>
+        <v>30.59568122427615</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6862796969101508</v>
+        <v>0.516216727072912</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1479,31 +1479,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.6942950527814089</v>
+        <v>0.2549277219735915</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6996</v>
+        <v>6907</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>780.1621672707291</v>
+        <v>781.8627969691015</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>197.5</v>
+        <v>141</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.17616191515894</v>
+        <v>55.04847974557215</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.59568105525484</v>
+        <v>29.74443408614899</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.516216727072912</v>
+        <v>0.6862796969101508</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1532,31 +1532,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2549277233091684</v>
+        <v>0.6942950527814089</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8039</v>
+        <v>7828</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>756.177136890076</v>
+        <v>762.8572808533252</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>149.5</v>
+        <v>1920</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1567,16 +1567,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.99184160427471</v>
+        <v>73.18891060409355</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.4639942420312</v>
+        <v>18.41873201907745</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.117713689007603</v>
+        <v>1.285728085332516</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1585,31 +1585,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.487896207936378</v>
+        <v>45.27731754734839</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6899</v>
+        <v>8039</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>731.6422747673743</v>
+        <v>756.177136890076</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>61.5</v>
+        <v>149.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.44072641438644</v>
+        <v>54.99184161120511</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.3460217506559</v>
+        <v>26.4639943333958</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.1642274767374211</v>
+        <v>1.117713689007603</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1638,11 +1638,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.5709587845424289</v>
+        <v>-1.48789620806039</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>724.7298403504723</v>
+        <v>739.7298403504723</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>505</v>
@@ -1701,21 +1701,21 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7827</v>
+        <v>6899</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>709.1928891006829</v>
+        <v>731.6422747673743</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>160</v>
+        <v>61.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1726,13 +1726,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.32311511764907</v>
+        <v>52.4407264262837</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.73455210917072</v>
+        <v>25.34602186642853</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4192889100682876</v>
+        <v>0.1642274767374211</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>1</v>
@@ -1744,31 +1744,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.020375528874119</v>
+        <v>-0.5709587846378226</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7750</v>
+        <v>7827</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>702.9739982648821</v>
+        <v>709.1928891006829</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2230</v>
+        <v>160</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1779,16 +1779,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>47.37767386624609</v>
+        <v>61.32311511764907</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.0575184367815</v>
+        <v>21.73455210917072</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7973998264882118</v>
+        <v>0.4192889100682876</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1797,31 +1797,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-43.3730656432022</v>
+        <v>1.020375528874119</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7780</v>
+        <v>7750</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>678.9318828820424</v>
+        <v>702.9739982648821</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>18.8</v>
+        <v>2230</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1832,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.89286899032182</v>
+        <v>47.377673866786</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.90192406219033</v>
+        <v>25.05751849493594</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.393188288204242</v>
+        <v>0.7973998264882118</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1850,31 +1850,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2210038415836543</v>
+        <v>-43.37306564501424</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7610</v>
+        <v>7780</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>677.959716532622</v>
+        <v>693.9318828820424</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1590</v>
+        <v>18.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.70709408550278</v>
+        <v>54.89286917760935</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>61.95889148382133</v>
+        <v>20.90192393916904</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7959716532622049</v>
+        <v>1.393188288204242</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1903,31 +1903,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-15.26912122409442</v>
+        <v>0.2210038403725849</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7744</v>
+        <v>7610</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>674.7166193656333</v>
+        <v>677.959716532622</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>493</v>
+        <v>1590</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1938,16 +1938,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.02881556596995</v>
+        <v>62.70709408550278</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16.11260058454811</v>
+        <v>61.95889148382133</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9716619365633276</v>
+        <v>0.7959716532622049</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1956,31 +1956,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0615858643475046</v>
+        <v>-15.26912122409442</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8032</v>
+        <v>7744</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>668.7897601473858</v>
+        <v>674.7166193656333</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>43.5</v>
+        <v>493</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1991,16 +1991,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.81798038516452</v>
+        <v>49.02881555639419</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.31128155224281</v>
+        <v>16.11260057301522</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3789760147385796</v>
+        <v>0.9716619365633276</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2009,31 +2009,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.4310528142663705</v>
+        <v>0.0615858647291887</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6965</v>
+        <v>8032</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>624.1480164590173</v>
+        <v>668.7897601473858</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2044,16 +2044,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.90829287628868</v>
+        <v>51.81798051431881</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.23150851948611</v>
+        <v>28.31128187780293</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4148016459017333</v>
+        <v>0.3789760147385796</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2062,31 +2062,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.6147632119361368</v>
+        <v>-0.4310528146384154</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6903</v>
+        <v>6965</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>620.0096295811835</v>
+        <v>639.1480164590173</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>397</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.46778531473922</v>
+        <v>55.90829316681389</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>19.25610989948265</v>
+        <v>22.2315084564983</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.000962958118349</v>
+        <v>0.4148016459017333</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2115,31 +2115,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-3.333084676460954</v>
+        <v>0.614763210695967</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7712</v>
+        <v>6903</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>608.8848916425136</v>
+        <v>620.0096295811835</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>142.5</v>
+        <v>397</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2150,16 +2150,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46.32296692967262</v>
+        <v>51.46778531668665</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.89785232661185</v>
+        <v>19.25611013755858</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3884891642513539</v>
+        <v>1.000962958118349</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2168,31 +2168,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-4.190795343884508</v>
+        <v>-3.333084676918902</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6906</v>
+        <v>7712</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>593.4979362660481</v>
+        <v>608.8848916425136</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>92.2</v>
+        <v>142.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.88408330804492</v>
+        <v>46.32296697288425</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>35.73523631094107</v>
+        <v>21.89785244096592</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3497936266048155</v>
+        <v>0.3884891642513539</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2221,31 +2221,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.764057556695946</v>
+        <v>-4.190795345124661</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6931</v>
+        <v>6906</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>574.979553425174</v>
+        <v>593.4979362660481</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>41.15</v>
+        <v>92.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>43.12537913867094</v>
+        <v>53.88408341628861</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.45543512289591</v>
+        <v>35.73523623939349</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4979553425174027</v>
+        <v>0.3497936266048155</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2274,31 +2274,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.4055706108728902</v>
+        <v>-1.764057557172944</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6894</v>
+        <v>6931</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>559.0227951595966</v>
+        <v>589.979553425174</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>349</v>
+        <v>41.15</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45.84065622649885</v>
+        <v>43.12537922246157</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.7332505885146</v>
+        <v>32.45543529407956</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4022795159596701</v>
+        <v>0.4979553425174027</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>1</v>
@@ -2327,31 +2327,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-5.451107162819186</v>
+        <v>0.4055706105676155</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7711</v>
+        <v>6894</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>538.7844657009132</v>
+        <v>559.0227951595966</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2362,16 +2362,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.40496188049803</v>
+        <v>45.84065625184099</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18.20946658960669</v>
+        <v>26.73325072439985</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3784465700913173</v>
+        <v>0.4022795159596701</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2380,31 +2380,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-6.132480457292956</v>
+        <v>-5.451107164631738</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6924</v>
+        <v>6916</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>530.2458997357785</v>
+        <v>540.134912428405</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>117</v>
+        <v>19.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2415,13 +2415,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>37.5020583846748</v>
+        <v>54.54728811543445</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>44.75934923755536</v>
+        <v>27.22050396592164</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.024589973577847</v>
+        <v>1.013491242840488</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2433,31 +2433,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-9.151246349591011</v>
+        <v>0.1774846543654106</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6916</v>
+        <v>7711</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>525.134912428405</v>
+        <v>538.7844657009132</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>19.6</v>
+        <v>359</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2468,13 +2468,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.54728839313233</v>
+        <v>44.40496188221694</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.22050420477196</v>
+        <v>18.20946668149526</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.013491242840488</v>
+        <v>0.3784465700913173</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1774846538979639</v>
+        <v>-6.132480457579147</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6861</v>
+        <v>6924</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>519.0616642657129</v>
+        <v>530.2458997357785</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>304</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2521,13 +2521,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>38.86742570119624</v>
+        <v>37.50205837197039</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>35.2995805041555</v>
+        <v>44.75934923755536</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.406166426571294</v>
+        <v>1.024589973577847</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2539,31 +2539,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-18.77933386405595</v>
+        <v>-9.151246349381148</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6890</v>
+        <v>6861</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>511.6384873419656</v>
+        <v>519.0616642657129</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2574,13 +2574,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>71.01426355117248</v>
+        <v>38.86742570383679</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>42.00841338763109</v>
+        <v>35.2995806955245</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1638487341965594</v>
+        <v>0.406166426571294</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2592,31 +2592,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>8.991888238979282</v>
+        <v>-18.77933386445667</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8040</v>
+        <v>6890</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>509.3482516064997</v>
+        <v>511.6384873419656</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>95.2</v>
+        <v>256</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2627,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>49.34245541329533</v>
+        <v>71.01426355117248</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>38.42220158885928</v>
+        <v>42.00841338763109</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4348251606499724</v>
+        <v>0.1638487341965594</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2645,31 +2645,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.215677468792008</v>
+        <v>8.991888238979282</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6902</v>
+        <v>8040</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>508.1768598879146</v>
+        <v>509.3482516064997</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>133</v>
+        <v>95.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2680,13 +2680,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.84439776212625</v>
+        <v>49.34245543439584</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>40.28634227269063</v>
+        <v>38.42220165451889</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3176859887914597</v>
+        <v>0.4348251606499724</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.122835049996312</v>
+        <v>-3.215677469192669</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7765</v>
+        <v>6902</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>505.374719368347</v>
+        <v>508.1768598879146</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>245.5</v>
+        <v>133</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>48.57086337061394</v>
+        <v>52.84439992284894</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>33.21389484921666</v>
+        <v>40.28634484524829</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5374719368346998</v>
+        <v>0.3176859887914597</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2751,31 +2751,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.857165094156166</v>
+        <v>-2.122835068980354</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6859</v>
+        <v>7765</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>500.0407619110457</v>
+        <v>505.374719368347</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>125</v>
+        <v>245.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.05087233540092</v>
+        <v>48.57086335981261</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24.23630293481606</v>
+        <v>33.21389486995012</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.004076191104569</v>
+        <v>0.5374719368346998</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2804,31 +2804,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.3481416810093281</v>
+        <v>-1.857165094823931</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6918</v>
+        <v>6859</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>483.8825951386297</v>
+        <v>500.0407619110457</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>73.3</v>
+        <v>125</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.84626594154159</v>
+        <v>51.05087244703749</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9.070415866578839</v>
+        <v>24.23630308070635</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3882595138629715</v>
+        <v>1.004076191104569</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2857,31 +2857,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.011514727523934</v>
+        <v>-0.3481416821541052</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7768</v>
+        <v>6918</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>478.1438681253589</v>
+        <v>483.8825951386297</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>378</v>
+        <v>73.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2892,16 +2892,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.10980818715755</v>
+        <v>46.84626579220009</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.49432684445235</v>
+        <v>9.070415898160109</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3143868125358912</v>
+        <v>0.3882595138629715</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2910,31 +2910,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.269825580910085</v>
+        <v>-0.0115147276193361</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6855</v>
+        <v>7768</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>466.7764856740154</v>
+        <v>478.1438681253589</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>126.5</v>
+        <v>378</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.68658556669776</v>
+        <v>45.10980821115939</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.30592346154639</v>
+        <v>16.49432685246702</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.1776485674015408</v>
+        <v>0.3143868125358912</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2963,31 +2963,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.286275210752807</v>
+        <v>-1.269825581577894</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6958</v>
+        <v>6925</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>464.1104318422929</v>
+        <v>466.9137579874425</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>17.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2998,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.72993703673042</v>
+        <v>46.80668538052578</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.77106986409033</v>
+        <v>27.24046594591908</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.411043184229294</v>
+        <v>0.6913757987442459</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3016,31 +3016,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0564613944359488</v>
+        <v>0.5238784723061443</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7732</v>
+        <v>6855</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>462.7841000048722</v>
+        <v>466.7764856740154</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>36</v>
+        <v>126.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.73707106607963</v>
+        <v>56.68658441102485</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.41529191144591</v>
+        <v>15.3059234622472</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2784100004872175</v>
+        <v>0.1776485674015408</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3069,31 +3069,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0005430706224374</v>
+        <v>0.286275210752807</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6937</v>
+        <v>6958</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>461.2319415376433</v>
+        <v>464.1104318422929</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>276.5</v>
+        <v>17.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>42.8519127728765</v>
+        <v>47.72993700868069</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.63849968715516</v>
+        <v>20.77106986887723</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6231941537643236</v>
+        <v>0.411043184229294</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3122,31 +3122,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-4.039124766122492</v>
+        <v>0.0564613943882486</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7753</v>
+        <v>7732</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>460.607962367113</v>
+        <v>462.7841000048722</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>42.35</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3157,13 +3157,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.70843798488475</v>
+        <v>53.73707109292052</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.13005376284863</v>
+        <v>13.41529193370785</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.0607962367113</v>
+        <v>0.2784100004872175</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3175,31 +3175,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1465798453579647</v>
+        <v>-0.0005430707273833</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7747</v>
+        <v>6937</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>458.170237649343</v>
+        <v>461.2319415376433</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>127</v>
+        <v>276.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3210,16 +3210,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.37628265179114</v>
+        <v>42.85191280966718</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9.230295611189378</v>
+        <v>15.63849985927888</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.317023764934301</v>
+        <v>0.6231941537643236</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3228,31 +3228,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.7374812384260343</v>
+        <v>-4.039124768316617</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7795</v>
+        <v>7753</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>452.2087316229014</v>
+        <v>460.607962367113</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>375</v>
+        <v>42.35</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3263,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.97187933462748</v>
+        <v>49.7084379255285</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15.484877462497</v>
+        <v>21.130053768517</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7208731622901393</v>
+        <v>2.0607962367113</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3281,31 +3281,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-3.885561456561167</v>
+        <v>-0.1465798452244073</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6925</v>
+        <v>7747</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>451.9137579874425</v>
+        <v>458.170237649343</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>127</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.80668540012381</v>
+        <v>51.37628264710848</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>27.24046596843369</v>
+        <v>9.230295575087244</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6913757987442459</v>
+        <v>2.317023764934301</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3334,31 +3334,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.5238784722489074</v>
+        <v>0.7374812377582565</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7738</v>
+        <v>7795</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>441.8543828323637</v>
+        <v>452.2087316229014</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>170.5</v>
+        <v>375</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3369,16 +3369,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.68952557441283</v>
+        <v>47.97187933109534</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.55413394846869</v>
+        <v>15.48487734500381</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6854382832363759</v>
+        <v>0.7208731622901393</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3387,31 +3387,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5652667828907383</v>
+        <v>-3.885561456370329</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6909</v>
+        <v>7738</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>440.9394429651246</v>
+        <v>441.8543828323637</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>44.35</v>
+        <v>170.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>33.5610800431983</v>
+        <v>48.68952555212456</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.97308408535397</v>
+        <v>20.55413400966828</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.593944296512459</v>
+        <v>0.6854382832363759</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3440,31 +3440,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.833355335643323</v>
+        <v>0.5652667829861455</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7734</v>
+        <v>7786</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>431.74698875803</v>
+        <v>441.4687849208649</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2780</v>
+        <v>127</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>37.78211081606065</v>
+        <v>53.4093679774164</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.56495685642648</v>
+        <v>19.38108194062445</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.174698875802998</v>
+        <v>1.146878492086497</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3493,31 +3493,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-83.10892122765549</v>
+        <v>1.66392740547967</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7704</v>
+        <v>6909</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>429.3588243033201</v>
+        <v>440.9394429651246</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>60.9</v>
+        <v>44.35</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3528,16 +3528,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.28262045318248</v>
+        <v>33.56108006409384</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.81795505161054</v>
+        <v>20.97308418207924</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4358824303320083</v>
+        <v>1.593944296512459</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3546,31 +3546,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.449183760554575</v>
+        <v>-0.83335533595814</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7730</v>
+        <v>7734</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>428.8928546105946</v>
+        <v>431.74698875803</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>180.5</v>
+        <v>2780</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3581,13 +3581,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.37638104607336</v>
+        <v>37.78211082480574</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.71388053674854</v>
+        <v>25.56495699300757</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3892854610594629</v>
+        <v>2.174698875802998</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3599,31 +3599,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-4.718263705964227</v>
+        <v>-83.10892123643218</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7786</v>
+        <v>7704</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>426.4687849208649</v>
+        <v>429.3588243033201</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>127</v>
+        <v>60.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3634,16 +3634,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>53.40936791324678</v>
+        <v>48.28262070421439</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.3810818987944</v>
+        <v>14.81795508798051</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.146878492086497</v>
+        <v>0.4358824303320083</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3652,31 +3652,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.663927406624419</v>
+        <v>-0.4491837614513098</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7705</v>
+        <v>7730</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>425.0933807226314</v>
+        <v>428.8928546105946</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>31.55</v>
+        <v>180.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3687,16 +3687,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.69803809664406</v>
+        <v>42.37638106996391</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.41023967958111</v>
+        <v>20.71388070865828</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5093380722631434</v>
+        <v>0.3892854610594629</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3705,31 +3705,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.127244794733756</v>
+        <v>-4.718263706784629</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8038</v>
+        <v>7705</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>424.6135014493271</v>
+        <v>425.0933807226314</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>41.4</v>
+        <v>31.55</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3740,16 +3740,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.34457901831322</v>
+        <v>47.69803802956189</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>9.763920474886024</v>
+        <v>20.4102396363724</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.961350144932708</v>
+        <v>0.5093380722631434</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3758,31 +3758,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0766462047627977</v>
+        <v>0.1272447947146756</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6913</v>
+        <v>8038</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>417.5032792103642</v>
+        <v>424.6135014493271</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>124.5</v>
+        <v>41.4</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3793,13 +3793,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.37354641578403</v>
+        <v>49.34457904449301</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.15285200280358</v>
+        <v>9.763920570194989</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2503279210364211</v>
+        <v>0.961350144932708</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3811,31 +3811,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.233376056149653</v>
+        <v>0.07664620466739951</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7805</v>
+        <v>6913</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>414.8806099717826</v>
+        <v>417.5032792103642</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>701</v>
+        <v>124.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3846,13 +3846,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>39.58503808614317</v>
+        <v>41.37354645548797</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30.0359276128329</v>
+        <v>20.15285211697324</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4880609971782658</v>
+        <v>0.2503279210364211</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-12.03380295215134</v>
+        <v>-2.233376056722035</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6862</v>
+        <v>7805</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>411.6235748102233</v>
+        <v>414.8806099717826</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>190</v>
+        <v>701</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.39381357567824</v>
+        <v>39.58503812525316</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.46635952558299</v>
+        <v>30.03592776394024</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6623574810223247</v>
+        <v>0.4880609971782658</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3917,31 +3917,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.983947996562935</v>
+        <v>-12.03380295291442</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7760</v>
+        <v>6862</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>410.8743527461241</v>
+        <v>411.6235748102233</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>32.15</v>
+        <v>190</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3952,16 +3952,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>38.00031268280768</v>
+        <v>50.39381360945577</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>58.00267243258273</v>
+        <v>23.46635958954366</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5874352746124096</v>
+        <v>0.6623574810223247</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3970,31 +3970,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1147035085436186</v>
+        <v>-0.9839479978031038</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7556</v>
+        <v>7760</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>410.0538808323726</v>
+        <v>410.8743527461241</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>273.5</v>
+        <v>32.15</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -4005,16 +4005,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.09172604156009</v>
+        <v>38.00031261350846</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.80609732360519</v>
+        <v>58.00267234461612</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5053880832372599</v>
+        <v>0.5874352746124096</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4023,31 +4023,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.092027328525888</v>
+        <v>0.1147035086008581</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7792</v>
+        <v>8047</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>408.8964399919968</v>
+        <v>410.4861264174447</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>257</v>
+        <v>51.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4058,16 +4058,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>37.07209713454611</v>
+        <v>53.79683764281543</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.24507526220753</v>
+        <v>8.724222420650459</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3896439991996754</v>
+        <v>0.5486126417444738</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4076,31 +4076,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.4604206677264812</v>
+        <v>1.109473453018972</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7822</v>
+        <v>7556</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>407.273590943246</v>
+        <v>410.0538808323726</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1000</v>
+        <v>273.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4111,16 +4111,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.32434245732718</v>
+        <v>50.0917260656606</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.29467297457212</v>
+        <v>17.80609750200781</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7273590943245991</v>
+        <v>0.5053880832372599</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4129,31 +4129,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-1.471145654592391</v>
+        <v>-2.092027329384478</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6887</v>
+        <v>7792</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>401.7447700277428</v>
+        <v>408.8964399919968</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>35.1</v>
+        <v>257</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.81440382669898</v>
+        <v>37.07209713019831</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8.041034342324371</v>
+        <v>23.24507526299834</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1744770027742807</v>
+        <v>0.3896439991996754</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4182,31 +4182,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.4298381996656945</v>
+        <v>-0.460420667821884</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8047</v>
+        <v>7822</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>395.4861264174447</v>
+        <v>407.273590943246</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>51.5</v>
+        <v>1000</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4217,16 +4217,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.79683764007137</v>
+        <v>40.32434246459504</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.724222300257962</v>
+        <v>15.29467310704321</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5486126417444738</v>
+        <v>0.7273590943245991</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4235,31 +4235,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.109473453085746</v>
+        <v>-1.471145657645053</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6914</v>
+        <v>7631</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>395.017636215438</v>
+        <v>406.5984320976953</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>142.5</v>
+        <v>125</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.62736634903472</v>
+        <v>51.52776260094203</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.69688334800572</v>
+        <v>11.36712536484906</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5017636215437998</v>
+        <v>1.159843209769534</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4288,31 +4288,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2564899145381347</v>
+        <v>1.692053124237706</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7703</v>
+        <v>6887</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>391.9548127125473</v>
+        <v>401.7447700277428</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>203.5</v>
+        <v>35.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4323,16 +4323,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.34189137153759</v>
+        <v>49.81440376165524</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.25965699660846</v>
+        <v>8.041034342614164</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6954812712547341</v>
+        <v>0.1744770027742807</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4341,31 +4341,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.9591103584465568</v>
+        <v>0.4298381996847663</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7631</v>
+        <v>6914</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>391.5984320976953</v>
+        <v>395.017636215438</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>125</v>
+        <v>142.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4376,16 +4376,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.52776260167308</v>
+        <v>48.62736642898481</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.36712557381713</v>
+        <v>15.69688332133128</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.159843209769534</v>
+        <v>0.5017636215437998</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4394,31 +4394,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.692053124409412</v>
+        <v>0.2564899144427379</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6865</v>
+        <v>7714</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>390.0213647967835</v>
+        <v>393.4421180333328</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4429,16 +4429,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.40992118191884</v>
+        <v>50.51844178391355</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>29.64609098156348</v>
+        <v>25.46467648805737</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.502136479678348</v>
+        <v>0.3442118033332742</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1158300015841296</v>
+        <v>0.8309296528551446</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6962</v>
+        <v>7703</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>384.7736620038214</v>
+        <v>391.9548127125473</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>35.8</v>
+        <v>203.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4482,16 +4482,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.25201804911922</v>
+        <v>48.34189136113611</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.13074368714482</v>
+        <v>16.25965711862903</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.477366200382143</v>
+        <v>0.6954812712547341</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4500,31 +4500,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.4283411339741368</v>
+        <v>-0.9591103591143436</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7714</v>
+        <v>7799</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>378.4421180333328</v>
+        <v>390.0361875039968</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>129</v>
+        <v>346</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4535,16 +4535,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.51844173301552</v>
+        <v>50.28857846501177</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.46467647229126</v>
+        <v>26.51819856655647</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3442118033332742</v>
+        <v>0.503618750399683</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4553,31 +4553,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.8309296535801629</v>
+        <v>3.283903413280712</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7717</v>
+        <v>6865</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>376.2024803949569</v>
+        <v>390.0213647967835</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>594</v>
+        <v>26</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4588,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.4977868842211</v>
+        <v>48.40992120339698</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.46636211378523</v>
+        <v>29.64609101582023</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.120248039495693</v>
+        <v>2.502136479678348</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4606,31 +4606,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-2.579669424909881</v>
+        <v>0.1158300015078124</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8033</v>
+        <v>7803</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>375.2081370738664</v>
+        <v>388.9298991590181</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>129.5</v>
+        <v>22.8</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4641,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.80367068976801</v>
+        <v>37.2629194621117</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7.950165023926123</v>
+        <v>23.00406678525906</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5208137073866317</v>
+        <v>0.3929899159018113</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4659,31 +4659,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.6051505216775852</v>
+        <v>0.198012066079839</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7799</v>
+        <v>6962</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>375.0361875039968</v>
+        <v>384.7736620038214</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>346</v>
+        <v>35.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4694,16 +4694,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.28857848156903</v>
+        <v>47.25201817593768</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>26.51819851052429</v>
+        <v>14.1307437582289</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.503618750399683</v>
+        <v>0.477366200382143</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4712,31 +4712,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>3.283903418336756</v>
+        <v>-0.4283411343175632</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7803</v>
+        <v>7717</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>373.9298991590181</v>
+        <v>376.2024803949569</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>22.8</v>
+        <v>594</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4747,13 +4747,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>37.26291934233446</v>
+        <v>42.4977868842211</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>23.00406673708863</v>
+        <v>14.46636211378523</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3929899159018113</v>
+        <v>1.120248039495693</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4765,31 +4765,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.198012066470971</v>
+        <v>-2.579669424909881</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7821</v>
+        <v>8033</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>367.2943262090122</v>
+        <v>375.2081370738664</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>44.45</v>
+        <v>129.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4800,16 +4800,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.59106620764173</v>
+        <v>41.80367070786937</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.10376004189162</v>
+        <v>7.950165219528918</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7294326209012251</v>
+        <v>0.5208137073866317</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4818,31 +4818,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.3846562261460666</v>
+        <v>-0.6051505220782616</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6936</v>
+        <v>7821</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>361.7393621975403</v>
+        <v>367.2943262090122</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>33.55</v>
+        <v>44.45</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4853,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.4483783289348</v>
+        <v>43.59106636723099</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.76939815275165</v>
+        <v>21.10376028549181</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6739362197540264</v>
+        <v>0.7294326209012251</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4871,31 +4871,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0400490343138349</v>
+        <v>0.384656225783559</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8034</v>
+        <v>6936</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>351.5143286817366</v>
+        <v>361.7393621975403</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>23.4</v>
+        <v>33.55</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4906,16 +4906,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.90625936726997</v>
+        <v>48.44837850632224</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.72692438226106</v>
+        <v>12.76939818103831</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6514328681736635</v>
+        <v>0.6739362197540264</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4924,31 +4924,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1078838719709018</v>
+        <v>0.040049034285218</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7772</v>
+        <v>8034</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>339.1706380326398</v>
+        <v>351.5143286817366</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>141</v>
+        <v>23.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.16685151138954</v>
+        <v>41.90625940607427</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.78146341796022</v>
+        <v>16.72692448625322</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4170638032639765</v>
+        <v>0.6514328681736635</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4977,31 +4977,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.308344292912517</v>
+        <v>-0.1078838720567597</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7751</v>
+        <v>7772</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>338.6711792868691</v>
+        <v>339.1706380326398</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1375</v>
+        <v>141</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5012,13 +5012,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>37.69219704704503</v>
+        <v>42.16685151138954</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.50764444817833</v>
+        <v>11.78146341796022</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8671179286869081</v>
+        <v>0.4170638032639765</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5030,31 +5030,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-28.62189056360634</v>
+        <v>-1.308344292912517</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7728</v>
+        <v>7751</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>327.6069599898044</v>
+        <v>338.6711792868691</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>714</v>
+        <v>1375</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5065,16 +5065,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.33940275328286</v>
+        <v>37.69219704600566</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.956476197835496</v>
+        <v>19.50764449440097</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7606959989804409</v>
+        <v>0.8671179286869081</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5083,31 +5083,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-2.913845945088823</v>
+        <v>-28.62189056446495</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6953</v>
+        <v>7728</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>327.0631187693833</v>
+        <v>327.6069599898044</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>233</v>
+        <v>714</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5118,16 +5118,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.48887598013136</v>
+        <v>46.33940277630763</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.04397864675919</v>
+        <v>9.956476221308655</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.206311876938332</v>
+        <v>0.7606959989804409</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5136,31 +5136,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-2.898196210491274</v>
+        <v>-2.913845950144869</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6923</v>
+        <v>6953</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>323.2532667975285</v>
+        <v>327.0631187693833</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>233</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.29672602559531</v>
+        <v>44.48887500946513</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.35623404935014</v>
+        <v>19.04397866373064</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3253266797528472</v>
+        <v>1.206311876938332</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5189,31 +5189,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1863080335182548</v>
+        <v>-2.898196211445238</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8046</v>
+        <v>6923</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>317.5129034584801</v>
+        <v>323.2532667975285</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>819</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5224,16 +5224,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.80936630029059</v>
+        <v>46.29672601942947</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.62381595890087</v>
+        <v>14.35623405096224</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.751290345848006</v>
+        <v>0.3253266797528472</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5242,31 +5242,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-11.71770609495905</v>
+        <v>0.1863080334991792</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7820</v>
+        <v>8046</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>314.5773508988849</v>
+        <v>317.5129034584801</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>117</v>
+        <v>819</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5277,16 +5277,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>31.65601185854095</v>
+        <v>46.80936630432826</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>31.76411237648887</v>
+        <v>18.62381612014336</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.457735089888491</v>
+        <v>0.751290345848006</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5295,31 +5295,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.4435990523077961</v>
+        <v>-11.71770609572225</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6967</v>
+        <v>7820</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>308.3534709316485</v>
+        <v>314.5773508988849</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>70.3</v>
+        <v>117</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5330,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.66695313914724</v>
+        <v>31.65601185854095</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9.881505434081944</v>
+        <v>31.76411237648887</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3353470931648459</v>
+        <v>0.457735089888491</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5348,31 +5348,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1077500860445618</v>
+        <v>0.4435990523077961</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6921</v>
+        <v>6895</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>302.9052371244609</v>
+        <v>312.2344617025655</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.7</v>
+        <v>164</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5383,13 +5383,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>33.13873914380856</v>
+        <v>53.87958359639555</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>26.41252388308151</v>
+        <v>20.52672519032471</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2905237124460855</v>
+        <v>0.7234461702565477</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5401,31 +5401,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.406974632874499</v>
+        <v>2.562437987262027</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6951</v>
+        <v>6967</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>302.7028355489105</v>
+        <v>308.3534709316485</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5436,16 +5436,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.97282710947994</v>
+        <v>45.66695315591422</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>27.16735256673607</v>
+        <v>9.881505379890818</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.270283554891049</v>
+        <v>0.3353470931648459</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5454,31 +5454,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.239468880788861</v>
+        <v>-0.1077500852241321</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6895</v>
+        <v>6921</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>297.2344617025655</v>
+        <v>302.9052371244609</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>164</v>
+        <v>69.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>53.87958355829369</v>
+        <v>33.13873914380856</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.5267251434022</v>
+        <v>26.41252388308151</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7234461702565477</v>
+        <v>0.2905237124460855</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5507,31 +5507,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>2.562437988025197</v>
+        <v>-0.406974632874499</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8011</v>
+        <v>6951</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>292.4896339936021</v>
+        <v>302.7028355489105</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.54577140594733</v>
+        <v>42.97282710455484</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.73314921494443</v>
+        <v>27.16735272701669</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7489633993602111</v>
+        <v>1.270283554891049</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>1</v>
@@ -5560,31 +5560,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0288064316413266</v>
+        <v>-0.2394688808651781</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7715</v>
+        <v>8011</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>288.3153185326018</v>
+        <v>292.4896339936021</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>27.7</v>
+        <v>18.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5595,16 +5595,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.5009332788948</v>
+        <v>46.545771483967</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.91363470182283</v>
+        <v>17.73314931456489</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8315318532601812</v>
+        <v>0.7489633993602111</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5613,31 +5613,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.018891610907073</v>
+        <v>0.0288064314982307</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6908</v>
+        <v>7715</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>286.7984673116414</v>
+        <v>288.3153185326018</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>38.9</v>
+        <v>27.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5648,16 +5648,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.6661667209078</v>
+        <v>45.5009332788948</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>10.4603675476441</v>
+        <v>19.9136348140599</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.179846731164143</v>
+        <v>0.8315318532601812</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5666,31 +5666,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.139011931702798</v>
+        <v>-0.0188916110120073</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6910</v>
+        <v>6908</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>283.5581809235436</v>
+        <v>286.7984673116414</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>28.55</v>
+        <v>38.9</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5701,13 +5701,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.1710938853001</v>
+        <v>45.66616691120344</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.53296382975697</v>
+        <v>10.46036757282306</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.85581809235436</v>
+        <v>0.179846731164143</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5719,31 +5719,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1131193024128545</v>
+        <v>0.1390119313116779</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6955</v>
+        <v>6910</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>282.7653248670057</v>
+        <v>283.5581809235436</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>138</v>
+        <v>28.55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5754,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.77146016105467</v>
+        <v>49.17109379909041</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4.492558714127553</v>
+        <v>14.53296382522463</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.276532486700575</v>
+        <v>0.85581809235436</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5772,31 +5772,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.307605206945974</v>
+        <v>0.1131193023937738</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6969</v>
+        <v>6955</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>279.3670095020103</v>
+        <v>282.7653248670057</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5807,16 +5807,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>35.46612563266359</v>
+        <v>48.77146016333771</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>20.08998545207042</v>
+        <v>4.492558727323156</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.436700950201033</v>
+        <v>1.276532486700575</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5825,31 +5825,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0660131096753126</v>
+        <v>0.307605206564372</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6994</v>
+        <v>6969</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>278.2510552535676</v>
+        <v>279.3670095020103</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>56.6</v>
+        <v>27</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5860,13 +5860,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.66544652983568</v>
+        <v>35.46612578743276</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>19.80409246576268</v>
+        <v>20.08998549389208</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3251055253567615</v>
+        <v>0.436700950201033</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>1</v>
@@ -5878,31 +5878,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1064274542838479</v>
+        <v>-0.066013109656235</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6928</v>
+        <v>6994</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>276.9360166041646</v>
+        <v>278.2510552535676</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>43.85</v>
+        <v>56.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5913,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.54338705197733</v>
+        <v>39.66544666537247</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.1436539820518</v>
+        <v>19.80409257786994</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.193601660416461</v>
+        <v>0.3251055253567615</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>1</v>
@@ -5931,31 +5931,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3815878447217742</v>
+        <v>-0.1064274555049347</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6997</v>
+        <v>6928</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>275.1083895767219</v>
+        <v>276.9360166041646</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0</v>
+        <v>43.85</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5966,16 +5966,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>23.56607869734</v>
+        <v>38.5433870904225</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.00832331105472</v>
+        <v>17.14365410270807</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.0108389576721941</v>
+        <v>1.193601660416461</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5984,31 +5984,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-4.626590109559539</v>
+        <v>-0.3815878450174994</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6877</v>
+        <v>6997</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>271.4519277305434</v>
+        <v>275.1083895767219</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6019,13 +6019,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>31.28561271739036</v>
+        <v>23.56607791448029</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.04772858557391</v>
+        <v>10.00832300670672</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6451927730543433</v>
+        <v>0.0108389576721941</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6037,31 +6037,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-3.918849658919301</v>
+        <v>-4.6265900900031</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6869</v>
+        <v>6877</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>268.4091661545837</v>
+        <v>271.4519277305434</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>130</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.38465324333775</v>
+        <v>31.28561275428692</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.18797027600868</v>
+        <v>20.04772877556029</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3409166154583636</v>
+        <v>0.6451927730543433</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6090,31 +6090,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.397836866181024</v>
+        <v>-3.918849659930541</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7740</v>
+        <v>6869</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>265.9812199064206</v>
+        <v>268.4091661545837</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>168.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6125,13 +6125,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.07252934292077</v>
+        <v>41.38465336993441</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.85093873980253</v>
+        <v>17.18797015590068</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5981219906420656</v>
+        <v>0.3409166154583636</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>1</v>
@@ -6143,31 +6143,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.4655855303181588</v>
+        <v>-0.3978368673257835</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6933</v>
+        <v>7740</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>253.5939496879953</v>
+        <v>265.9812199064206</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>150.5</v>
+        <v>168.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.37124826168041</v>
+        <v>46.07252936105415</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.77665243796438</v>
+        <v>10.85093878844071</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3593949687995363</v>
+        <v>0.5981219906420656</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6196,31 +6196,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-2.862006376828164</v>
+        <v>-0.4655855316537414</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6983</v>
+        <v>6933</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>252.6978349341288</v>
+        <v>253.5939496879953</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>348.5</v>
+        <v>150.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6231,13 +6231,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.63151159327897</v>
+        <v>41.37124829485512</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.20889645549262</v>
+        <v>17.77665241054335</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.2697834934128824</v>
+        <v>0.3593949687995363</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.805993898026742</v>
+        <v>-2.862006378545314</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6259,21 +6259,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7736</v>
+        <v>6983</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>251.1971617934597</v>
+        <v>252.6978349341288</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>348.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6284,13 +6284,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.1143331266731</v>
+        <v>41.63151226570238</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.27816225811488</v>
+        <v>15.20889727915117</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6197161793459688</v>
+        <v>0.2697834934128824</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6302,31 +6302,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1878017551903019</v>
+        <v>-1.805993919014132</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6952</v>
+        <v>7736</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>250.874573763311</v>
+        <v>251.1971617934597</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>36.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6337,13 +6337,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.6400061083673</v>
+        <v>45.11433335979929</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.30299526253795</v>
+        <v>17.27816226198764</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5874573763311055</v>
+        <v>0.6197161793459688</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0230810592231141</v>
+        <v>0.1878017545225208</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6885</v>
+        <v>6952</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>235.5903401426825</v>
+        <v>250.874573763311</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>23.05</v>
+        <v>36.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.33927249608464</v>
+        <v>40.6400061083673</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>25.87543082387615</v>
+        <v>19.30299531165488</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5590340142682472</v>
+        <v>0.5874573763311055</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6408,31 +6408,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1003669416178525</v>
+        <v>0.0230810591277186</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6919</v>
+        <v>6885</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>235.1801451838762</v>
+        <v>235.5903401426825</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>92.7</v>
+        <v>23.05</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6443,16 +6443,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.64855296146145</v>
+        <v>48.3392725549484</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.9113682949289</v>
+        <v>25.87543093264432</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5180145183876189</v>
+        <v>0.5590340142682472</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6461,31 +6461,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.66513179012395</v>
+        <v>0.1003669414270581</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7842</v>
+        <v>6919</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>235.0935165001199</v>
+        <v>235.1801451838762</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>103</v>
+        <v>92.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6496,16 +6496,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>34.0798737855266</v>
+        <v>42.64855372305</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>27.09624830373308</v>
+        <v>13.91136852576689</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5093516500119918</v>
+        <v>0.5180145183876189</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6514,31 +6514,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.9961073317394612</v>
+        <v>-0.66513179937516</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6863</v>
+        <v>7842</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>220.9922587555751</v>
+        <v>235.0935165001199</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>95.3</v>
+        <v>103</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6549,16 +6549,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>36.53535254047353</v>
+        <v>34.0798737855266</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>22.32383673610962</v>
+        <v>27.09624830373308</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5992258755575028</v>
+        <v>0.5093516500119918</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.004592314751858</v>
+        <v>0.9961073317394612</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8024</v>
+        <v>6863</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>220.9921159524559</v>
+        <v>220.9922587555751</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>12.1</v>
+        <v>95.3</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6602,13 +6602,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>36.05600372849255</v>
+        <v>36.53535278145177</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>21.42972106712035</v>
+        <v>22.32383679489625</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5992115952455895</v>
+        <v>0.5992258755575028</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>1</v>
@@ -6620,7 +6620,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0312123861916893</v>
+        <v>-2.004592316659801</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6630,21 +6630,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6854</v>
+        <v>8024</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>217.4123513203062</v>
+        <v>220.9921159524559</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>133</v>
+        <v>12.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6655,16 +6655,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.98491030567855</v>
+        <v>36.05600378680179</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.18920745548389</v>
+        <v>21.42972112162219</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2412351320306198</v>
+        <v>0.5992115952455895</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6673,31 +6673,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-2.124185120948817</v>
+        <v>-0.0312123862393879</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7770</v>
+        <v>6854</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>212.9513138616888</v>
+        <v>217.4123513203062</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6708,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.97519556469604</v>
+        <v>38.98491031899428</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6.932141404006591</v>
+        <v>16.18920757415696</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2951313861688784</v>
+        <v>0.2412351320306198</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6726,31 +6726,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0026243746765728</v>
+        <v>-2.12418512266597</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7823</v>
+        <v>7770</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>212.4900189214313</v>
+        <v>212.9513138616888</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>83.5</v>
+        <v>42</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6761,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>30.46071759679407</v>
+        <v>46.97519932771517</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>28.75931933051219</v>
+        <v>6.932139646152139</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2490018921431323</v>
+        <v>0.2951313861688784</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6779,31 +6779,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-2.456260308453188</v>
+        <v>-0.0026243898065679</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7547</v>
+        <v>7823</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>211.0427982017339</v>
+        <v>212.4900189214313</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>59.5</v>
+        <v>83.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6814,16 +6814,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.62274497051918</v>
+        <v>30.46071759679407</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.06049168935067</v>
+        <v>28.75931933051219</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.1042798201733911</v>
+        <v>0.2490018921431323</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6832,31 +6832,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.3508182307702272</v>
+        <v>-2.456260308453188</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6988</v>
+        <v>7547</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>200.4349388725179</v>
+        <v>211.0427982017339</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>13.9</v>
+        <v>59.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6867,13 +6867,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>32.28686477652359</v>
+        <v>39.62274500343389</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.28791164901725</v>
+        <v>16.06049174263893</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.543493887251788</v>
+        <v>0.1042798201733911</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6885,31 +6885,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.2486752345501293</v>
+        <v>-0.3508182310945762</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6873</v>
+        <v>6988</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>197.0855902536261</v>
+        <v>200.4349388725179</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>81.7</v>
+        <v>13.9</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6920,13 +6920,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>38.26365167924639</v>
+        <v>32.28686488750215</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.36409232370733</v>
+        <v>20.28791177433337</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7085590253626063</v>
+        <v>0.543493887251788</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6938,31 +6938,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.9748116265369432</v>
+        <v>-0.2486752347218461</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>8045</v>
+        <v>6873</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>194.7787737657613</v>
+        <v>197.0855902536261</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>62</v>
+        <v>81.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6973,16 +6973,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>38.7373486247747</v>
+        <v>38.26365181463493</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>16.81758374157859</v>
+        <v>14.3640923546347</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4778773765761313</v>
+        <v>0.7085590253626063</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6991,31 +6991,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.532345850375866</v>
+        <v>-0.9748116265369432</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7810</v>
+        <v>8045</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>191.5702573228506</v>
+        <v>194.7787737657613</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>204.5</v>
+        <v>62</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7026,16 +7026,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.36079513991619</v>
+        <v>38.73734867126834</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.21475390656485</v>
+        <v>16.81758374843993</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1570257322850577</v>
+        <v>0.4778773765761313</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7044,31 +7044,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-3.673835984908413</v>
+        <v>-0.5323458514633832</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7818</v>
+        <v>7810</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>177.8430475957529</v>
+        <v>191.5702573228505</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>61.9</v>
+        <v>204.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7079,16 +7079,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>24.5724541805997</v>
+        <v>39.36079514354293</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46.86033427917551</v>
+        <v>17.21475390656485</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.2843047595752863</v>
+        <v>0.1570257322850577</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7097,31 +7097,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>1.010267503521792</v>
+        <v>-3.673835985003807</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7791</v>
+        <v>7818</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>164.1979281730529</v>
+        <v>177.8430475957529</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7132,13 +7132,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>38.29058989844245</v>
+        <v>24.57245414031414</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>26.50907711376835</v>
+        <v>46.86033428294209</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.419792817305286</v>
+        <v>0.2843047595752863</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>1</v>
@@ -7150,7 +7150,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.4493956517315807</v>
+        <v>1.010267503521792</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6934</v>
+        <v>7791</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>163.5077727198483</v>
+        <v>164.1979281730529</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>70</v>
+        <v>62.8</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7185,16 +7185,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>37.9928200388804</v>
+        <v>38.29058990810253</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>32.19453885093665</v>
+        <v>26.50907717016597</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.3507772719848309</v>
+        <v>0.419792817305286</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.004759199163713</v>
+        <v>-0.4493956519605301</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>7402</v>
+        <v>6934</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>158.1626088611822</v>
+        <v>163.5077727198483</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>89.7</v>
+        <v>70</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7238,16 +7238,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>29.19377029722166</v>
+        <v>37.99281838578827</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>20.0112473305953</v>
+        <v>32.19453879928615</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.316260886118225</v>
+        <v>0.3507772719848309</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.1837573841839619</v>
+        <v>-0.0047591986676449</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7266,52 +7266,105 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>邑錡</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>158.1626088611822</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>29.19377029990714</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>20.01124746135094</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>1.316260886118225</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.1837573846800273</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
         <v>6971</v>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>惠民實業</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D129" s="2" t="n">
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
         <v>155.3972895793058</v>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E130" s="2" t="n">
         <v>26.55</v>
       </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>34.42747052926478</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>15.99543155756578</v>
-      </c>
-      <c r="J129" s="2" t="n">
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>34.42747059597549</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>15.99543155756579</v>
+      </c>
+      <c r="J130" s="2" t="n">
         <v>0.5397289579305811</v>
       </c>
-      <c r="K129" s="2" t="n">
+      <c r="K130" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>-0.0032770688003268</v>
-      </c>
-      <c r="O129" s="2" t="inlineStr">
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.0032770688957225</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
